--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_364_R37.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_364_R37.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.8496</v>
+        <v>11.506</v>
       </c>
       <c r="E2" t="n">
-        <v>8.642099999999999</v>
+        <v>8.996</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2075</v>
+        <v>2.51</v>
       </c>
       <c r="G2" t="n">
         <v>5.6658</v>
@@ -610,13 +610,13 @@
         <v>3.0154</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.4967</v>
+        <v>-0.8404</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8962</v>
+        <v>-0.5423</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6005</v>
+        <v>-0.2981</v>
       </c>
       <c r="V2" t="n">
         <v>4.8249</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. FAYE</t>
+          <t>S. HERRERA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.5855</v>
+        <v>5.4271</v>
       </c>
       <c r="E3" t="n">
-        <v>3.963</v>
+        <v>4.3975</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6225</v>
+        <v>1.0296</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1321</v>
+        <v>4.5429</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8175</v>
+        <v>1.8428</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3147</v>
+        <v>2.7001</v>
       </c>
       <c r="J3" t="n">
-        <v>1.9926</v>
+        <v>3.8676</v>
       </c>
       <c r="K3" t="n">
-        <v>1.8822</v>
+        <v>1.4788</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1104</v>
+        <v>2.3888</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1396</v>
+        <v>0.6753</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.06469999999999999</v>
+        <v>0.364</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2042</v>
+        <v>0.3113</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9278</v>
+        <v>2.3195</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9278</v>
+        <v>2.3195</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8477</v>
+        <v>-1.2935</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6869</v>
+        <v>-0.5423</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1608</v>
+        <v>-0.7512</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6778999999999999</v>
+        <v>-0.1418</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2836</v>
+        <v>1.0722</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3943</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. HERRERA</t>
+          <t>N. HIFI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5953</v>
+        <v>4.4561</v>
       </c>
       <c r="E4" t="n">
-        <v>3.969</v>
+        <v>3.7349</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6263</v>
+        <v>0.7212</v>
       </c>
       <c r="G4" t="n">
-        <v>4.5429</v>
+        <v>5.565</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8428</v>
+        <v>0.7635</v>
       </c>
       <c r="I4" t="n">
-        <v>2.7001</v>
+        <v>4.8015</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8676</v>
+        <v>5.3005</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4788</v>
+        <v>0.8605</v>
       </c>
       <c r="L4" t="n">
-        <v>2.3888</v>
+        <v>4.44</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6753</v>
+        <v>0.2645</v>
       </c>
       <c r="N4" t="n">
-        <v>0.364</v>
+        <v>-0.097</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3113</v>
+        <v>0.3615</v>
       </c>
       <c r="P4" t="n">
-        <v>2.3195</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3195</v>
+        <v>0.9278</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.1253</v>
+        <v>-0.7894</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9709</v>
+        <v>-0.3183</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.1545</v>
+        <v>-0.4711</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="W4" t="n">
         <v>1.0722</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. HIFI</t>
+          <t>M. FAYE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.203</v>
+        <v>3.834</v>
       </c>
       <c r="E5" t="n">
-        <v>3.3811</v>
+        <v>2.5476</v>
       </c>
       <c r="F5" t="n">
-        <v>0.822</v>
+        <v>1.2864</v>
       </c>
       <c r="G5" t="n">
-        <v>5.565</v>
+        <v>2.1321</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7635</v>
+        <v>1.8175</v>
       </c>
       <c r="I5" t="n">
-        <v>4.8015</v>
+        <v>0.3147</v>
       </c>
       <c r="J5" t="n">
-        <v>5.3005</v>
+        <v>1.9926</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8605</v>
+        <v>1.8822</v>
       </c>
       <c r="L5" t="n">
-        <v>4.44</v>
+        <v>0.1104</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2645</v>
+        <v>0.1396</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.097</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3615</v>
+        <v>0.2042</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0.9278</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0425</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6721</v>
+        <v>0.2715</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3703</v>
+        <v>-0.1753</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0722</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0722</v>
+        <v>0.2836</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.5654</v>
+        <v>3.4899</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6803</v>
+        <v>-0.2517</v>
       </c>
       <c r="F6" t="n">
-        <v>4.2457</v>
+        <v>3.7416</v>
       </c>
       <c r="G6" t="n">
         <v>2.8024</v>
@@ -922,13 +922,13 @@
         <v>3.0154</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8632</v>
+        <v>-0.9388</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1202</v>
+        <v>-0.6917</v>
       </c>
       <c r="U6" t="n">
-        <v>0.257</v>
+        <v>-0.2471</v>
       </c>
       <c r="V6" t="n">
         <v>0.9304</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. DOKOSSI</t>
+          <t>A. M'BAYE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.7482</v>
+        <v>2.6507</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.241</v>
+        <v>1.764</v>
       </c>
       <c r="F7" t="n">
-        <v>2.9892</v>
+        <v>0.8867</v>
       </c>
       <c r="G7" t="n">
-        <v>4.9889</v>
+        <v>2.1021</v>
       </c>
       <c r="H7" t="n">
-        <v>2.9913</v>
+        <v>0.7838000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>1.9976</v>
+        <v>1.3183</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2734</v>
+        <v>1.9091</v>
       </c>
       <c r="K7" t="n">
-        <v>2.4269</v>
+        <v>1.163</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8465</v>
+        <v>0.746</v>
       </c>
       <c r="M7" t="n">
-        <v>1.7155</v>
+        <v>0.1931</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5644</v>
+        <v>-0.3792</v>
       </c>
       <c r="O7" t="n">
-        <v>1.1511</v>
+        <v>0.5723</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5515</v>
+        <v>1.1598</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2407</v>
+        <v>-0.753</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0351</v>
+        <v>-0.2869</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2056</v>
+        <v>-0.4661</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="W7" t="n">
+        <v>0.1418</v>
+      </c>
+      <c r="X7" t="n">
         <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-1.0722</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. M'BAYE</t>
+          <t>L. STEVENS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,40 +1033,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.0787</v>
+        <v>2.235</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5281</v>
+        <v>2.5487</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5507</v>
+        <v>-0.3137</v>
       </c>
       <c r="G8" t="n">
-        <v>2.1021</v>
+        <v>1.3874</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7838000000000001</v>
+        <v>0.5977</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3183</v>
+        <v>0.7897</v>
       </c>
       <c r="J8" t="n">
-        <v>1.9091</v>
+        <v>1.2586</v>
       </c>
       <c r="K8" t="n">
-        <v>1.163</v>
+        <v>0.8304</v>
       </c>
       <c r="L8" t="n">
-        <v>0.746</v>
+        <v>0.4282</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1931</v>
+        <v>0.1288</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3792</v>
+        <v>-0.2327</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5723</v>
+        <v>0.3615</v>
       </c>
       <c r="P8" t="n">
         <v>1.1598</v>
@@ -1078,28 +1078,28 @@
         <v>1.1598</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3249</v>
+        <v>-0.8483000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5228</v>
+        <v>-0.3183</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8022</v>
+        <v>-0.53</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1418</v>
+        <v>0.5361</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1418</v>
+        <v>1.6083</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. STEVENS</t>
+          <t>A. DOKOSSI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.5787</v>
+        <v>2.1927</v>
       </c>
       <c r="E9" t="n">
-        <v>2.1948</v>
+        <v>-0.5949</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6161</v>
+        <v>2.7876</v>
       </c>
       <c r="G9" t="n">
-        <v>1.3874</v>
+        <v>4.9889</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5977</v>
+        <v>2.9913</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7897</v>
+        <v>1.9976</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2586</v>
+        <v>3.2734</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8304</v>
+        <v>2.4269</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4282</v>
+        <v>0.8465</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1288</v>
+        <v>1.7155</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2327</v>
+        <v>0.5644</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3615</v>
+        <v>1.1511</v>
       </c>
       <c r="P9" t="n">
-        <v>1.1598</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q9" t="n">
+        <v>-3.4793</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.5515</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-0.7962</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-0.389</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-0.4072</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-1.0722</v>
+      </c>
+      <c r="W9" t="n">
         <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.1598</v>
-      </c>
-      <c r="S9" t="n">
-        <v>-1.5046</v>
-      </c>
-      <c r="T9" t="n">
-        <v>-0.6721</v>
-      </c>
-      <c r="U9" t="n">
-        <v>-0.8325</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0.5361</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.6083</v>
       </c>
       <c r="X9" t="n">
         <v>-1.0722</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.906</v>
+        <v>0.6029</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5823</v>
+        <v>0.3464</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3238</v>
+        <v>0.2566</v>
       </c>
       <c r="G10" t="n">
         <v>0.8507</v>
@@ -1234,13 +1234,13 @@
         <v>2.0876</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2539</v>
+        <v>-0.0492</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1889</v>
+        <v>-0.047</v>
       </c>
       <c r="U10" t="n">
-        <v>0.065</v>
+        <v>-0.0022</v>
       </c>
       <c r="V10" t="n">
         <v>-2.2862</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L. CAVALIERE</t>
+          <t>D. HOMMES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3024</v>
+        <v>-0.0746</v>
       </c>
       <c r="E11" t="n">
-        <v>0.08550000000000001</v>
+        <v>-0.273</v>
       </c>
       <c r="F11" t="n">
-        <v>0.217</v>
+        <v>0.1984</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7375</v>
+        <v>1.9987</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.611</v>
+        <v>0.3123</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3485</v>
+        <v>1.6864</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2452</v>
+        <v>1.2483</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.0181</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7729</v>
+        <v>1.1643</v>
       </c>
       <c r="M11" t="n">
-        <v>0.9827</v>
+        <v>0.7503</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4071</v>
+        <v>0.2283</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5756</v>
+        <v>0.5221</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
+        <v>-1.1598</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.1598</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-0.465</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-0.3615</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0.1034</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-1.6083</v>
+      </c>
+      <c r="W11" t="n">
         <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.6959</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.3356</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.1889</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0.1467</v>
-      </c>
-      <c r="V11" t="n">
-        <v>-1.4665</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0.1418</v>
       </c>
       <c r="X11" t="n">
         <v>-1.6083</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. HOMMES</t>
+          <t>L. CAVALIERE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.486</v>
+        <v>-0.3635</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.5835</v>
+        <v>-0.3117</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0975</v>
+        <v>-0.0519</v>
       </c>
       <c r="G12" t="n">
-        <v>1.9987</v>
+        <v>0.7375</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3123</v>
+        <v>-0.611</v>
       </c>
       <c r="I12" t="n">
-        <v>1.6864</v>
+        <v>1.3485</v>
       </c>
       <c r="J12" t="n">
-        <v>1.2483</v>
+        <v>-0.2452</v>
       </c>
       <c r="K12" t="n">
-        <v>0.08400000000000001</v>
+        <v>-1.0181</v>
       </c>
       <c r="L12" t="n">
-        <v>1.1643</v>
+        <v>0.7729</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7503</v>
+        <v>0.9827</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2283</v>
+        <v>0.4071</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5221</v>
+        <v>0.5756</v>
       </c>
       <c r="P12" t="n">
+        <v>0.6959</v>
+      </c>
+      <c r="Q12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>-1.1598</v>
-      </c>
       <c r="R12" t="n">
-        <v>1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8764</v>
+        <v>-0.3304</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6721</v>
+        <v>-0.2082</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2043</v>
+        <v>-0.1221</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.6083</v>
+        <v>-1.4665</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X12" t="n">
         <v>-1.6083</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.3007</v>
+        <v>-2.9565</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.4121</v>
+        <v>-3.1015</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1113</v>
+        <v>0.1449</v>
       </c>
       <c r="G13" t="n">
         <v>-2.5365</v>
@@ -1468,13 +1468,13 @@
         <v>0.6959</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3183</v>
+        <v>-0.9741</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7468</v>
+        <v>-0.4362</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5715</v>
+        <v>-0.5379</v>
       </c>
       <c r="V13" t="n">
         <v>-0.1418</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>32.6261</v>
+        <v>32.9998</v>
       </c>
       <c r="E14" t="n">
-        <v>19.429</v>
+        <v>19.8023</v>
       </c>
       <c r="F14" t="n">
         <v>13.1974</v>
@@ -1546,13 +1546,13 @@
         <v>19.7162</v>
       </c>
       <c r="S14" t="n">
-        <v>-8.355399999999999</v>
+        <v>-7.9821</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.243600000000001</v>
+        <v>-3.8702</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.1119</v>
+        <v>-4.111700000000001</v>
       </c>
       <c r="V14" t="n">
         <v>1.466500000000001</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>O. BRISSETT</t>
+          <t>J. DOWTIN JR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1568</v>
+        <v>2.6359</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3746</v>
+        <v>1.7363</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2179</v>
+        <v>0.8996</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.7603</v>
+        <v>-1.815</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.4525</v>
+        <v>-0.0349</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3079</v>
+        <v>-1.7801</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6018</v>
+        <v>-0.7678</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6421</v>
+        <v>0.3767</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.0403</v>
+        <v>-1.1445</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3621</v>
+        <v>-1.0472</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0945</v>
+        <v>-0.4116</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2676</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1644</v>
+        <v>1.9353</v>
       </c>
       <c r="T15" t="n">
-        <v>1.4119</v>
+        <v>1.1483</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7524999999999999</v>
+        <v>0.787</v>
       </c>
       <c r="V15" t="n">
-        <v>2.1444</v>
+        <v>1.3558</v>
       </c>
       <c r="W15" t="n">
-        <v>2.6805</v>
+        <v>1.3558</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. DOWTIN JR</t>
+          <t>O. BRISSETT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9961</v>
+        <v>1.0451</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2645</v>
+        <v>1.431</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7316</v>
+        <v>-0.3859</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.815</v>
+        <v>-0.7603</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0349</v>
+        <v>-0.4525</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.7801</v>
+        <v>-0.3079</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.7678</v>
+        <v>0.6018</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3767</v>
+        <v>0.6421</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.1445</v>
+        <v>-0.0403</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0472</v>
+        <v>-1.3621</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4116</v>
+        <v>-1.0945</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-0.2676</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2955</v>
+        <v>1.0528</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6765</v>
+        <v>0.4683</v>
       </c>
       <c r="U16" t="n">
-        <v>0.619</v>
+        <v>0.5845</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3558</v>
+        <v>2.1444</v>
       </c>
       <c r="W16" t="n">
-        <v>1.3558</v>
+        <v>2.6805</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3359</v>
+        <v>0.1337</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9632</v>
+        <v>1.7273</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.6273</v>
+        <v>-1.5936</v>
       </c>
       <c r="G17" t="n">
         <v>-2.6277</v>
@@ -1780,13 +1780,13 @@
         <v>0.6959</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3528</v>
+        <v>0.1505</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1968</v>
+        <v>-0.0391</v>
       </c>
       <c r="U17" t="n">
-        <v>0.156</v>
+        <v>0.1896</v>
       </c>
       <c r="V17" t="n">
         <v>3.0748</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0861</v>
+        <v>-0.0655</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9852</v>
+        <v>1.8673</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.8992</v>
+        <v>-1.9328</v>
       </c>
       <c r="G18" t="n">
         <v>1.7652</v>
@@ -1858,13 +1858,13 @@
         <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>1.625</v>
+        <v>1.4734</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9243</v>
+        <v>0.8063</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7007</v>
+        <v>0.6671</v>
       </c>
       <c r="V18" t="n">
         <v>-2.1444</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0365</v>
+        <v>-0.8012</v>
       </c>
       <c r="E19" t="n">
         <v>0.1153</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1518</v>
+        <v>-0.9166</v>
       </c>
       <c r="G19" t="n">
         <v>-1.8385</v>
@@ -1936,13 +1936,13 @@
         <v>1.1598</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6603</v>
+        <v>0.8955</v>
       </c>
       <c r="T19" t="n">
         <v>0.5272</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1331</v>
+        <v>0.3684</v>
       </c>
       <c r="V19" t="n">
         <v>0.1418</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.861</v>
+        <v>-2.911</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1653</v>
+        <v>-2.0474</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6956</v>
+        <v>-0.8637</v>
       </c>
       <c r="G20" t="n">
         <v>-2.5275</v>
@@ -2014,13 +2014,13 @@
         <v>0.6959</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3598</v>
+        <v>0.3097</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1766</v>
+        <v>-0.0587</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5364</v>
+        <v>0.3684</v>
       </c>
       <c r="V20" t="n">
         <v>0.9304</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. SORKIN</t>
+          <t>J. HOARD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.0074</v>
+        <v>-4.8178</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.0697</v>
+        <v>-3.2368</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.9378</v>
+        <v>-1.5809</v>
       </c>
       <c r="G21" t="n">
-        <v>-6.374</v>
+        <v>-5.9612</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.9615</v>
+        <v>-4.7333</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.4124</v>
+        <v>-1.2279</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.7541</v>
+        <v>-2.4866</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.0782</v>
+        <v>-2.4732</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-0.0134</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.6199</v>
+        <v>-3.4745</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8834</v>
+        <v>-2.2601</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.7365</v>
+        <v>-1.2144</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>2.3665</v>
+        <v>0.7697000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>1.8442</v>
+        <v>0.2677</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5223</v>
+        <v>0.5019</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5361</v>
+        <v>0.1418</v>
       </c>
       <c r="W21" t="n">
+        <v>0.1418</v>
+      </c>
+      <c r="X21" t="n">
         <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>-0.5361</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. HOARD</t>
+          <t>J. DIBARTOLOMEO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.0721</v>
+        <v>-5.6867</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.0625</v>
+        <v>-0.1883</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0096</v>
+        <v>-5.4983</v>
       </c>
       <c r="G22" t="n">
-        <v>-5.9612</v>
+        <v>-3.6311</v>
       </c>
       <c r="H22" t="n">
-        <v>-4.7333</v>
+        <v>-0.7334000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.2279</v>
+        <v>-2.8977</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.4866</v>
+        <v>-0.6722</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.4732</v>
+        <v>-0.6687</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.0134</v>
+        <v>-0.0035</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.4745</v>
+        <v>-2.9588</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.2601</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.2144</v>
+        <v>-2.8942</v>
       </c>
       <c r="P22" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>1.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5153</v>
+        <v>0.8415</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5579</v>
+        <v>0.4839</v>
       </c>
       <c r="U22" t="n">
-        <v>1.0732</v>
+        <v>0.3576</v>
       </c>
       <c r="V22" t="n">
-        <v>0.1418</v>
+        <v>-4.2888</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-4.2888</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. DIBARTOLOMEO</t>
+          <t>R. SORKIN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.175</v>
+        <v>-6.1698</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5422</v>
+        <v>-4.1312</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.6328</v>
+        <v>-2.0386</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.6311</v>
+        <v>-6.374</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7334000000000001</v>
+        <v>-3.9615</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.8977</v>
+        <v>-2.4124</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6722</v>
+        <v>-3.7541</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6687</v>
+        <v>-3.0782</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.0035</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.9588</v>
+        <v>-2.6199</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.8834</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.8942</v>
+        <v>-1.7365</v>
       </c>
       <c r="P23" t="n">
-        <v>1.3917</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3532</v>
+        <v>1.2041</v>
       </c>
       <c r="T23" t="n">
-        <v>0.13</v>
+        <v>0.7826</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2232</v>
+        <v>0.4215</v>
       </c>
       <c r="V23" t="n">
-        <v>-4.2888</v>
+        <v>-0.5361</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-4.2888</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.271699999999999</v>
+        <v>-7.8677</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.0353</v>
+        <v>-4.7994</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.2364</v>
+        <v>-3.0683</v>
       </c>
       <c r="G24" t="n">
         <v>-1.3789</v>
@@ -2326,13 +2326,13 @@
         <v>0.232</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.112</v>
+        <v>0.2919</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0905</v>
+        <v>0.3264</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2025</v>
+        <v>-0.0345</v>
       </c>
       <c r="V24" t="n">
         <v>-1.214</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.7774</v>
+        <v>-8.1211</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.5613</v>
+        <v>-6.2074</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.2161</v>
+        <v>-1.9137</v>
       </c>
       <c r="G25" t="n">
         <v>-5.0883</v>
@@ -2404,13 +2404,13 @@
         <v>0.9278</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.2252</v>
+        <v>-0.5689</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.955</v>
+        <v>-0.6012</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2702</v>
+        <v>0.0323</v>
       </c>
       <c r="V25" t="n">
         <v>-1.0722</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-32.6262</v>
+        <v>-32.6261</v>
       </c>
       <c r="E26" t="n">
-        <v>-13.7335</v>
+        <v>-13.7333</v>
       </c>
       <c r="F26" t="n">
-        <v>-18.8929</v>
+        <v>-18.8928</v>
       </c>
       <c r="G26" t="n">
         <v>-30.2373</v>
@@ -2458,7 +2458,7 @@
         <v>-7.9518</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.442599999999999</v>
+        <v>-1.4426</v>
       </c>
       <c r="L26" t="n">
         <v>-6.5092</v>
@@ -2482,13 +2482,13 @@
         <v>10.4381</v>
       </c>
       <c r="S26" t="n">
-        <v>8.355599999999999</v>
+        <v>8.355500000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>4.1119</v>
+        <v>4.111699999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>4.2437</v>
+        <v>4.2438</v>
       </c>
       <c r="V26" t="n">
         <v>-1.4665</v>
